--- a/data/trans_bre/P1426-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1426-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,0</t>
+          <t>-0,98; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>308,13%</t>
+          <t>405,14%</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,07</t>
+          <t>-1,11; 0,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,72</t>
+          <t>0,16; 1,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,36</t>
+          <t>0,13; 2,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-85,14%</t>
+          <t>-80,04%</t>
         </is>
       </c>
     </row>
@@ -794,22 +794,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,0</t>
+          <t>-0,97; 0,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,27</t>
+          <t>-0,14; 1,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,4</t>
+          <t>-2,54; -0,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-85,0; 414,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-98,38; -27,0</t>
+          <t>-100,0; -10,82</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,59%</t>
+          <t>-31,76%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,37</t>
+          <t>-0,66; 1,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,53</t>
+          <t>-1,61; 0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,45</t>
+          <t>-2,68; 0,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,31; 573,17</t>
+          <t>-67,33; 586,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,71; 106,87</t>
+          <t>-88,76; 111,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,47; 106,99</t>
+          <t>-61,51; 23,31</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-35,94%</t>
+          <t>-29,72%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,66</t>
+          <t>-3,14; 0,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,6</t>
+          <t>-1,94; 2,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,14</t>
+          <t>-3,85; 0,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-83,11; 68,74</t>
+          <t>-83,66; 60,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 208,7</t>
+          <t>-55,62; 238,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,96; 6,92</t>
+          <t>-55,14; 6,99</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-4,24</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-48,32%</t>
+          <t>-20,08%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -0,84</t>
+          <t>-7,07; -0,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,74</t>
+          <t>2,13; 7,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -0,9</t>
+          <t>-4,57; 1,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-87,96; -14,85</t>
+          <t>-87,74; -9,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,27; 894,28</t>
+          <t>58,66; 1043,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,45; -10,23</t>
+          <t>-43,97; 22,61</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,46</t>
+          <t>1,38; 9,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 0,9</t>
+          <t>-7,0; 0,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,55</t>
+          <t>-4,35; 4,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,68; 354,84</t>
+          <t>17,22; 376,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 18,51</t>
+          <t>-64,8; 10,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 25,17</t>
+          <t>-18,89; 27,75</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,98</t>
+          <t>-0,4; 0,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,2</t>
+          <t>-0,03; 1,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,08</t>
+          <t>-0,84; 0,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 78,93</t>
+          <t>-21,86; 79,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 102,25</t>
+          <t>-0,86; 113,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 28,85</t>
+          <t>-16,28; 18,02</t>
         </is>
       </c>
     </row>
